--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96212</v>
+        <v>96215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96215</v>
+        <v>96216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40833-2022 artfynd.xlsx
+++ b/artfynd/A 40833-2022 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>55107358</v>
       </c>
       <c r="B5" t="n">
-        <v>96216</v>
+        <v>96221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
